--- a/stranded-travellers-saga/sorrow flows down the irrawaddy/outline/world.xlsx
+++ b/stranded-travellers-saga/sorrow flows down the irrawaddy/outline/world.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="characters" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="events" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="chapters" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="88">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -138,6 +139,153 @@
   </si>
   <si>
     <t xml:space="preserve">Supportive Friend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The High Priestess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Aye Thawdar] connects with Amy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Htet Yan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Htet Yan] arrives in Bagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Fool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amy informs [Aye Thawdar] that Htet Yan made a discovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Magician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Htet Yan] and Aye Thawdar meet and interpret the evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Aye Thawdar] and Htet Yan find a new letter about Yu Wai's journey in helping Anawrahta won the throne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hermit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Htet Yan] and Aye Thawdar find out Yu Wai spent the rest of his life as a hermit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Chariot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Aye Thawdar] and Htet Yan find out the rise of Thuriya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Htet Yan] and Aye Thawdar almost consider the case closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Lovers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amy reveals to [Aye Thawdar] about the feelings Yu Wai had for Waddy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Empress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Htet Yan] and Aye Thawdar find out about Thuriya's confession about his love for Aye Thawdar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Death</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Aye Thawdar] and Htet Yan find the tomb of Yu Wai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Moon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Htet Yan] and Aye Thawdar find out Thuriya was the one that killed Yu Wai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Aye Thawdar] gets stung by a scorpion. Htet Yan takes care of her</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judgement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As described by Aye Thawdar's fever dream, Htet Yan finds the letter written by Yu Wai that he forgives Thuriya for killing him</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Devil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Aye Thawdar] gets better and they find out that Thuriya regrets killing Yu Wai because he didn't know how to stop Kyansittha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Htet Yan] and Aye Thawdar find out Thuriya misunderstood Yu Wai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Aye Thawdar] and Htet Yan find the tomb of Thuriya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hierophant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Htet Yan] and Aye Thawdar spend a few days in the tomb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wheel of Fortune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On their way back,[Aye Thawdar] and Htet Yan get caught by armed forces who's been looking for the tomb of Thuriya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hanged Man</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Htet Yan] and Aye Thawdar decide to give up the treasures of Thuriya in exchange for their lives. The leader of the armed force takes Aye Thawdar away and Htet Yan ends up screaming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Star</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The leader of the armed force confess that he's from the bloodline of Thuriya with a few clues passed through generations. He gives Thuriya's ring back to [Aye Thawdar]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Htet Yan] is relieved to see Aye Thawdar is safe. They travel back to Yangon. Htet Yan hears the tale of Thuriya from Aye Thawdar and feels like he's a reincarnation of Thuriya but he keeps it to himself and go back to Bangkok</t>
   </si>
 </sst>
 </file>
@@ -147,7 +295,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,7 +334,20 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Noto Sans Devanagari"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Padauk"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Padauk"/>
       <family val="0"/>
       <charset val="1"/>
@@ -234,25 +395,29 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -447,7 +612,7 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.15"/>
@@ -455,57 +620,57 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="32.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="7.57"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="2" width="8.68"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="8.68"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -514,21 +679,21 @@
       <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -537,70 +702,70 @@
       <c r="C4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -635,4 +800,352 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="6.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="12.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="9.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="33.62"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="5" width="11.55"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="24.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="24.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="36.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="36.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="36.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="36.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="36.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="48.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>